--- a/cypress/downloads/EmployersList.xlsx
+++ b/cypress/downloads/EmployersList.xlsx
@@ -197,8 +197,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Grid" displayName="Grid" ref="A1:K6" totalsRowShown="0">
-  <x:autoFilter ref="A1:K6"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Grid" displayName="Grid" ref="A1:K7" totalsRowShown="0">
+  <x:autoFilter ref="A1:K7"/>
   <x:tableColumns count="11">
     <x:tableColumn id="1" name="Name"/>
     <x:tableColumn id="2" name="Email"/>
@@ -504,7 +504,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:K6"/>
+  <x:dimension ref="A1:K7"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
     <x:row r="1" spans="1:11">
@@ -579,7 +579,28 @@
     </x:row>
     <x:row r="3" spans="1:11">
       <x:c r="A3" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="B3" s="0" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="C3" s="0" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="D3" s="0" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="E3" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="F3" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="G3" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="H3" s="0" t="s">
+        <x:v>18</x:v>
       </x:c>
       <x:c r="I3" s="0" t="s">
         <x:v>19</x:v>
@@ -588,15 +609,12 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="K3" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:11">
       <x:c r="A4" s="0" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="H4" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="I4" s="0" t="s">
         <x:v>19</x:v>
@@ -610,22 +628,10 @@
     </x:row>
     <x:row r="5" spans="1:11">
       <x:c r="A5" s="0" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="B5" s="0" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="D5" s="0" t="s">
-        <x:v>28</x:v>
-      </x:c>
-      <x:c r="F5" s="0" t="s">
-        <x:v>29</x:v>
-      </x:c>
-      <x:c r="G5" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="H5" s="0" t="s">
-        <x:v>31</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="I5" s="0" t="s">
         <x:v>19</x:v>
@@ -634,38 +640,67 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="K5" s="0" t="s">
-        <x:v>32</x:v>
+        <x:v>23</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:11">
       <x:c r="A6" s="0" t="s">
-        <x:v>33</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="B6" s="0" t="s">
-        <x:v>34</x:v>
-      </x:c>
-      <x:c r="C6" s="0" t="s">
-        <x:v>35</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="D6" s="0" t="s">
-        <x:v>36</x:v>
-      </x:c>
-      <x:c r="E6" s="0" t="s">
-        <x:v>18</x:v>
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="F6" s="0" t="s">
+        <x:v>29</x:v>
       </x:c>
       <x:c r="G6" s="0" t="s">
-        <x:v>37</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="H6" s="0" t="s">
-        <x:v>38</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="I6" s="0" t="s">
-        <x:v>39</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="J6" s="0" t="s">
         <x:v>20</x:v>
       </x:c>
       <x:c r="K6" s="0" t="s">
+        <x:v>32</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7" spans="1:11">
+      <x:c r="A7" s="0" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="B7" s="0" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="C7" s="0" t="s">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="D7" s="0" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="E7" s="0" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="G7" s="0" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="H7" s="0" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="I7" s="0" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="J7" s="0" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="K7" s="0" t="s">
         <x:v>32</x:v>
       </x:c>
     </x:row>

--- a/cypress/downloads/EmployersList.xlsx
+++ b/cypress/downloads/EmployersList.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="40">
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="41">
   <x:si>
     <x:t>Name</x:t>
   </x:si>
@@ -82,10 +82,13 @@
     <x:t>Accredited</x:t>
   </x:si>
   <x:si>
+    <x:t>mlian</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Unaccredited</x:t>
+  </x:si>
+  <x:si>
     <x:t>test123</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Unaccredited</x:t>
   </x:si>
   <x:si>
     <x:t>test new em1</x:t>
@@ -579,28 +582,7 @@
     </x:row>
     <x:row r="3" spans="1:11">
       <x:c r="A3" s="0" t="s">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="B3" s="0" t="s">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="C3" s="0" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="D3" s="0" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="E3" s="0" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="F3" s="0" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="G3" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="H3" s="0" t="s">
-        <x:v>18</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="I3" s="0" t="s">
         <x:v>19</x:v>
@@ -609,12 +591,12 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="K3" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>23</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:11">
       <x:c r="A4" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="I4" s="0" t="s">
         <x:v>19</x:v>
@@ -628,10 +610,10 @@
     </x:row>
     <x:row r="5" spans="1:11">
       <x:c r="A5" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="H5" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="I5" s="0" t="s">
         <x:v>19</x:v>
@@ -645,22 +627,22 @@
     </x:row>
     <x:row r="6" spans="1:11">
       <x:c r="A6" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="B6" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="D6" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="F6" s="0" t="s">
-        <x:v>29</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="G6" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="H6" s="0" t="s">
-        <x:v>31</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="I6" s="0" t="s">
         <x:v>19</x:v>
@@ -669,39 +651,39 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="K6" s="0" t="s">
-        <x:v>32</x:v>
+        <x:v>33</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:11">
       <x:c r="A7" s="0" t="s">
-        <x:v>33</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="B7" s="0" t="s">
-        <x:v>34</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="C7" s="0" t="s">
-        <x:v>35</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="D7" s="0" t="s">
-        <x:v>36</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="E7" s="0" t="s">
         <x:v>18</x:v>
       </x:c>
       <x:c r="G7" s="0" t="s">
-        <x:v>37</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="H7" s="0" t="s">
-        <x:v>38</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="I7" s="0" t="s">
-        <x:v>39</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="J7" s="0" t="s">
         <x:v>20</x:v>
       </x:c>
       <x:c r="K7" s="0" t="s">
-        <x:v>32</x:v>
+        <x:v>33</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/cypress/downloads/EmployersList.xlsx
+++ b/cypress/downloads/EmployersList.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="41">
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="40">
   <x:si>
     <x:t>Name</x:t>
   </x:si>
@@ -85,12 +85,12 @@
     <x:t>mlian</x:t>
   </x:si>
   <x:si>
+    <x:t>test123</x:t>
+  </x:si>
+  <x:si>
     <x:t>Unaccredited</x:t>
   </x:si>
   <x:si>
-    <x:t>test123</x:t>
-  </x:si>
-  <x:si>
     <x:t>test new em1</x:t>
   </x:si>
   <x:si>
@@ -134,9 +134,6 @@
   </x:si>
   <x:si>
     <x:t>2332</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Supplier</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -591,12 +588,12 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="K3" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:11">
       <x:c r="A4" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="I4" s="0" t="s">
         <x:v>19</x:v>
@@ -605,7 +602,7 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="K4" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>24</x:v>
       </x:c>
     </x:row>
     <x:row r="5" spans="1:11">
@@ -622,7 +619,7 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="K5" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>24</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:11">
@@ -677,13 +674,13 @@
         <x:v>39</x:v>
       </x:c>
       <x:c r="I7" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="J7" s="0" t="s">
         <x:v>20</x:v>
       </x:c>
       <x:c r="K7" s="0" t="s">
-        <x:v>33</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/cypress/downloads/EmployersList.xlsx
+++ b/cypress/downloads/EmployersList.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="40">
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="39">
   <x:si>
     <x:t>Name</x:t>
   </x:si>
@@ -79,16 +79,13 @@
     <x:t>No</x:t>
   </x:si>
   <x:si>
-    <x:t>Accredited</x:t>
+    <x:t>Unaccredited</x:t>
   </x:si>
   <x:si>
     <x:t>mlian</x:t>
   </x:si>
   <x:si>
     <x:t>test123</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Unaccredited</x:t>
   </x:si>
   <x:si>
     <x:t>test new em1</x:t>
@@ -602,15 +599,15 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="K4" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="5" spans="1:11">
       <x:c r="A5" s="0" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="H5" s="0" t="s">
         <x:v>25</x:v>
-      </x:c>
-      <x:c r="H5" s="0" t="s">
-        <x:v>26</x:v>
       </x:c>
       <x:c r="I5" s="0" t="s">
         <x:v>19</x:v>
@@ -619,27 +616,27 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="K5" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:11">
       <x:c r="A6" s="0" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="B6" s="0" t="s">
         <x:v>27</x:v>
       </x:c>
-      <x:c r="B6" s="0" t="s">
+      <x:c r="D6" s="0" t="s">
         <x:v>28</x:v>
       </x:c>
-      <x:c r="D6" s="0" t="s">
+      <x:c r="F6" s="0" t="s">
         <x:v>29</x:v>
       </x:c>
-      <x:c r="F6" s="0" t="s">
+      <x:c r="G6" s="0" t="s">
         <x:v>30</x:v>
       </x:c>
-      <x:c r="G6" s="0" t="s">
+      <x:c r="H6" s="0" t="s">
         <x:v>31</x:v>
-      </x:c>
-      <x:c r="H6" s="0" t="s">
-        <x:v>32</x:v>
       </x:c>
       <x:c r="I6" s="0" t="s">
         <x:v>19</x:v>
@@ -648,30 +645,30 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="K6" s="0" t="s">
-        <x:v>33</x:v>
+        <x:v>32</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:11">
       <x:c r="A7" s="0" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="B7" s="0" t="s">
         <x:v>34</x:v>
       </x:c>
-      <x:c r="B7" s="0" t="s">
+      <x:c r="C7" s="0" t="s">
         <x:v>35</x:v>
       </x:c>
-      <x:c r="C7" s="0" t="s">
+      <x:c r="D7" s="0" t="s">
         <x:v>36</x:v>
-      </x:c>
-      <x:c r="D7" s="0" t="s">
-        <x:v>37</x:v>
       </x:c>
       <x:c r="E7" s="0" t="s">
         <x:v>18</x:v>
       </x:c>
       <x:c r="G7" s="0" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="H7" s="0" t="s">
         <x:v>38</x:v>
-      </x:c>
-      <x:c r="H7" s="0" t="s">
-        <x:v>39</x:v>
       </x:c>
       <x:c r="I7" s="0" t="s">
         <x:v>19</x:v>

--- a/cypress/downloads/EmployersList.xlsx
+++ b/cypress/downloads/EmployersList.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="39">
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="38">
   <x:si>
     <x:t>Name</x:t>
   </x:si>
@@ -88,10 +88,7 @@
     <x:t>test123</x:t>
   </x:si>
   <x:si>
-    <x:t>test new em1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>21</x:t>
+    <x:t>test new em</x:t>
   </x:si>
   <x:si>
     <x:t>recruiter emp</x:t>
@@ -606,9 +603,6 @@
       <x:c r="A5" s="0" t="s">
         <x:v>24</x:v>
       </x:c>
-      <x:c r="H5" s="0" t="s">
-        <x:v>25</x:v>
-      </x:c>
       <x:c r="I5" s="0" t="s">
         <x:v>19</x:v>
       </x:c>
@@ -621,22 +615,22 @@
     </x:row>
     <x:row r="6" spans="1:11">
       <x:c r="A6" s="0" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="B6" s="0" t="s">
         <x:v>26</x:v>
       </x:c>
-      <x:c r="B6" s="0" t="s">
+      <x:c r="D6" s="0" t="s">
         <x:v>27</x:v>
       </x:c>
-      <x:c r="D6" s="0" t="s">
+      <x:c r="F6" s="0" t="s">
         <x:v>28</x:v>
       </x:c>
-      <x:c r="F6" s="0" t="s">
+      <x:c r="G6" s="0" t="s">
         <x:v>29</x:v>
       </x:c>
-      <x:c r="G6" s="0" t="s">
+      <x:c r="H6" s="0" t="s">
         <x:v>30</x:v>
-      </x:c>
-      <x:c r="H6" s="0" t="s">
-        <x:v>31</x:v>
       </x:c>
       <x:c r="I6" s="0" t="s">
         <x:v>19</x:v>
@@ -645,30 +639,30 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="K6" s="0" t="s">
-        <x:v>32</x:v>
+        <x:v>31</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:11">
       <x:c r="A7" s="0" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="B7" s="0" t="s">
         <x:v>33</x:v>
       </x:c>
-      <x:c r="B7" s="0" t="s">
+      <x:c r="C7" s="0" t="s">
         <x:v>34</x:v>
       </x:c>
-      <x:c r="C7" s="0" t="s">
+      <x:c r="D7" s="0" t="s">
         <x:v>35</x:v>
-      </x:c>
-      <x:c r="D7" s="0" t="s">
-        <x:v>36</x:v>
       </x:c>
       <x:c r="E7" s="0" t="s">
         <x:v>18</x:v>
       </x:c>
       <x:c r="G7" s="0" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="H7" s="0" t="s">
         <x:v>37</x:v>
-      </x:c>
-      <x:c r="H7" s="0" t="s">
-        <x:v>38</x:v>
       </x:c>
       <x:c r="I7" s="0" t="s">
         <x:v>19</x:v>

--- a/cypress/downloads/EmployersList.xlsx
+++ b/cypress/downloads/EmployersList.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="38">
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="39">
   <x:si>
     <x:t>Name</x:t>
   </x:si>
@@ -79,10 +79,13 @@
     <x:t>No</x:t>
   </x:si>
   <x:si>
+    <x:t>Accredited</x:t>
+  </x:si>
+  <x:si>
+    <x:t>mlian</x:t>
+  </x:si>
+  <x:si>
     <x:t>Unaccredited</x:t>
-  </x:si>
-  <x:si>
-    <x:t>mlian</x:t>
   </x:si>
   <x:si>
     <x:t>test123</x:t>
@@ -582,12 +585,12 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="K3" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>23</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:11">
       <x:c r="A4" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="I4" s="0" t="s">
         <x:v>19</x:v>
@@ -596,12 +599,12 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="K4" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>23</x:v>
       </x:c>
     </x:row>
     <x:row r="5" spans="1:11">
       <x:c r="A5" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="I5" s="0" t="s">
         <x:v>19</x:v>
@@ -610,27 +613,27 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="K5" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>23</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:11">
       <x:c r="A6" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="B6" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="D6" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="F6" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="G6" s="0" t="s">
-        <x:v>29</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="H6" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="I6" s="0" t="s">
         <x:v>19</x:v>
@@ -639,30 +642,30 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="K6" s="0" t="s">
-        <x:v>31</x:v>
+        <x:v>32</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:11">
       <x:c r="A7" s="0" t="s">
-        <x:v>32</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="B7" s="0" t="s">
-        <x:v>33</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C7" s="0" t="s">
-        <x:v>34</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="D7" s="0" t="s">
-        <x:v>35</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="E7" s="0" t="s">
         <x:v>18</x:v>
       </x:c>
       <x:c r="G7" s="0" t="s">
-        <x:v>36</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="H7" s="0" t="s">
-        <x:v>37</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="I7" s="0" t="s">
         <x:v>19</x:v>
@@ -671,7 +674,7 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="K7" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>23</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/cypress/downloads/EmployersList.xlsx
+++ b/cypress/downloads/EmployersList.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="39">
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="38">
   <x:si>
     <x:t>Name</x:t>
   </x:si>
@@ -83,9 +83,6 @@
   </x:si>
   <x:si>
     <x:t>mlian</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Unaccredited</x:t>
   </x:si>
   <x:si>
     <x:t>test123</x:t>
@@ -585,12 +582,12 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="K3" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:11">
       <x:c r="A4" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="I4" s="0" t="s">
         <x:v>19</x:v>
@@ -599,12 +596,12 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="K4" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="5" spans="1:11">
       <x:c r="A5" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="I5" s="0" t="s">
         <x:v>19</x:v>
@@ -613,27 +610,27 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="K5" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:11">
       <x:c r="A6" s="0" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="B6" s="0" t="s">
         <x:v>26</x:v>
       </x:c>
-      <x:c r="B6" s="0" t="s">
+      <x:c r="D6" s="0" t="s">
         <x:v>27</x:v>
       </x:c>
-      <x:c r="D6" s="0" t="s">
+      <x:c r="F6" s="0" t="s">
         <x:v>28</x:v>
       </x:c>
-      <x:c r="F6" s="0" t="s">
+      <x:c r="G6" s="0" t="s">
         <x:v>29</x:v>
       </x:c>
-      <x:c r="G6" s="0" t="s">
+      <x:c r="H6" s="0" t="s">
         <x:v>30</x:v>
-      </x:c>
-      <x:c r="H6" s="0" t="s">
-        <x:v>31</x:v>
       </x:c>
       <x:c r="I6" s="0" t="s">
         <x:v>19</x:v>
@@ -642,30 +639,30 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="K6" s="0" t="s">
-        <x:v>32</x:v>
+        <x:v>31</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:11">
       <x:c r="A7" s="0" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="B7" s="0" t="s">
         <x:v>33</x:v>
       </x:c>
-      <x:c r="B7" s="0" t="s">
+      <x:c r="C7" s="0" t="s">
         <x:v>34</x:v>
       </x:c>
-      <x:c r="C7" s="0" t="s">
+      <x:c r="D7" s="0" t="s">
         <x:v>35</x:v>
-      </x:c>
-      <x:c r="D7" s="0" t="s">
-        <x:v>36</x:v>
       </x:c>
       <x:c r="E7" s="0" t="s">
         <x:v>18</x:v>
       </x:c>
       <x:c r="G7" s="0" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="H7" s="0" t="s">
         <x:v>37</x:v>
-      </x:c>
-      <x:c r="H7" s="0" t="s">
-        <x:v>38</x:v>
       </x:c>
       <x:c r="I7" s="0" t="s">
         <x:v>19</x:v>
@@ -674,7 +671,7 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="K7" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/cypress/downloads/EmployersList.xlsx
+++ b/cypress/downloads/EmployersList.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="38">
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="39">
   <x:si>
     <x:t>Name</x:t>
   </x:si>
@@ -82,6 +82,12 @@
     <x:t>Accredited</x:t>
   </x:si>
   <x:si>
+    <x:t>lets see</x:t>
+  </x:si>
+  <x:si>
+    <x:t>N/A</x:t>
+  </x:si>
+  <x:si>
     <x:t>mlian</x:t>
   </x:si>
   <x:si>
@@ -107,9 +113,6 @@
   </x:si>
   <x:si>
     <x:t>323</x:t>
-  </x:si>
-  <x:si>
-    <x:t>N/A</x:t>
   </x:si>
   <x:si>
     <x:t>supplier emp</x:t>
@@ -191,8 +194,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Grid" displayName="Grid" ref="A1:K7" totalsRowShown="0">
-  <x:autoFilter ref="A1:K7"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Grid" displayName="Grid" ref="A1:K8" totalsRowShown="0">
+  <x:autoFilter ref="A1:K8"/>
   <x:tableColumns count="11">
     <x:tableColumn id="1" name="Name"/>
     <x:tableColumn id="2" name="Email"/>
@@ -498,7 +501,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:K7"/>
+  <x:dimension ref="A1:K8"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
     <x:row r="1" spans="1:11">
@@ -582,12 +585,12 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="K3" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>23</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:11">
       <x:c r="A4" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="I4" s="0" t="s">
         <x:v>19</x:v>
@@ -601,7 +604,7 @@
     </x:row>
     <x:row r="5" spans="1:11">
       <x:c r="A5" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="I5" s="0" t="s">
         <x:v>19</x:v>
@@ -615,22 +618,7 @@
     </x:row>
     <x:row r="6" spans="1:11">
       <x:c r="A6" s="0" t="s">
-        <x:v>25</x:v>
-      </x:c>
-      <x:c r="B6" s="0" t="s">
         <x:v>26</x:v>
-      </x:c>
-      <x:c r="D6" s="0" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="F6" s="0" t="s">
-        <x:v>28</x:v>
-      </x:c>
-      <x:c r="G6" s="0" t="s">
-        <x:v>29</x:v>
-      </x:c>
-      <x:c r="H6" s="0" t="s">
-        <x:v>30</x:v>
       </x:c>
       <x:c r="I6" s="0" t="s">
         <x:v>19</x:v>
@@ -639,30 +627,27 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="K6" s="0" t="s">
-        <x:v>31</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:11">
       <x:c r="A7" s="0" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="B7" s="0" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="D7" s="0" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="F7" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="G7" s="0" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="H7" s="0" t="s">
         <x:v>32</x:v>
-      </x:c>
-      <x:c r="B7" s="0" t="s">
-        <x:v>33</x:v>
-      </x:c>
-      <x:c r="C7" s="0" t="s">
-        <x:v>34</x:v>
-      </x:c>
-      <x:c r="D7" s="0" t="s">
-        <x:v>35</x:v>
-      </x:c>
-      <x:c r="E7" s="0" t="s">
-        <x:v>18</x:v>
-      </x:c>
-      <x:c r="G7" s="0" t="s">
-        <x:v>36</x:v>
-      </x:c>
-      <x:c r="H7" s="0" t="s">
-        <x:v>37</x:v>
       </x:c>
       <x:c r="I7" s="0" t="s">
         <x:v>19</x:v>
@@ -671,6 +656,38 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="K7" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8" spans="1:11">
+      <x:c r="A8" s="0" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="B8" s="0" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="C8" s="0" t="s">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="D8" s="0" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="E8" s="0" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="G8" s="0" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="H8" s="0" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="I8" s="0" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="J8" s="0" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="K8" s="0" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>

--- a/cypress/downloads/EmployersList.xlsx
+++ b/cypress/downloads/EmployersList.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="39">
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="41">
   <x:si>
     <x:t>Name</x:t>
   </x:si>
@@ -82,10 +82,16 @@
     <x:t>Accredited</x:t>
   </x:si>
   <x:si>
+    <x:t>nimal</x:t>
+  </x:si>
+  <x:si>
+    <x:t>N/A</x:t>
+  </x:si>
+  <x:si>
+    <x:t>employer</x:t>
+  </x:si>
+  <x:si>
     <x:t>lets see</x:t>
-  </x:si>
-  <x:si>
-    <x:t>N/A</x:t>
   </x:si>
   <x:si>
     <x:t>mlian</x:t>
@@ -194,8 +200,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Grid" displayName="Grid" ref="A1:K8" totalsRowShown="0">
-  <x:autoFilter ref="A1:K8"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Grid" displayName="Grid" ref="A1:K10" totalsRowShown="0">
+  <x:autoFilter ref="A1:K10"/>
   <x:tableColumns count="11">
     <x:tableColumn id="1" name="Name"/>
     <x:tableColumn id="2" name="Email"/>
@@ -501,7 +507,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:K8"/>
+  <x:dimension ref="A1:K10"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
     <x:row r="1" spans="1:11">
@@ -599,7 +605,7 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="K4" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>23</x:v>
       </x:c>
     </x:row>
     <x:row r="5" spans="1:11">
@@ -613,7 +619,7 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="K5" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>23</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:11">
@@ -634,21 +640,6 @@
       <x:c r="A7" s="0" t="s">
         <x:v>27</x:v>
       </x:c>
-      <x:c r="B7" s="0" t="s">
-        <x:v>28</x:v>
-      </x:c>
-      <x:c r="D7" s="0" t="s">
-        <x:v>29</x:v>
-      </x:c>
-      <x:c r="F7" s="0" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="G7" s="0" t="s">
-        <x:v>31</x:v>
-      </x:c>
-      <x:c r="H7" s="0" t="s">
-        <x:v>32</x:v>
-      </x:c>
       <x:c r="I7" s="0" t="s">
         <x:v>19</x:v>
       </x:c>
@@ -656,38 +647,81 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="K7" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:11">
       <x:c r="A8" s="0" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="I8" s="0" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="J8" s="0" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="K8" s="0" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" spans="1:11">
+      <x:c r="A9" s="0" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="B9" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="D9" s="0" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="F9" s="0" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="G9" s="0" t="s">
         <x:v>33</x:v>
       </x:c>
-      <x:c r="B8" s="0" t="s">
+      <x:c r="H9" s="0" t="s">
         <x:v>34</x:v>
       </x:c>
-      <x:c r="C8" s="0" t="s">
+      <x:c r="I9" s="0" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="J9" s="0" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="K9" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" spans="1:11">
+      <x:c r="A10" s="0" t="s">
         <x:v>35</x:v>
       </x:c>
-      <x:c r="D8" s="0" t="s">
+      <x:c r="B10" s="0" t="s">
         <x:v>36</x:v>
       </x:c>
-      <x:c r="E8" s="0" t="s">
+      <x:c r="C10" s="0" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="D10" s="0" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="E10" s="0" t="s">
         <x:v>18</x:v>
       </x:c>
-      <x:c r="G8" s="0" t="s">
-        <x:v>37</x:v>
-      </x:c>
-      <x:c r="H8" s="0" t="s">
-        <x:v>38</x:v>
-      </x:c>
-      <x:c r="I8" s="0" t="s">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c r="J8" s="0" t="s">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="K8" s="0" t="s">
+      <x:c r="G10" s="0" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="H10" s="0" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="I10" s="0" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="J10" s="0" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="K10" s="0" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>

--- a/cypress/downloads/EmployersList.xlsx
+++ b/cypress/downloads/EmployersList.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="41">
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="44">
   <x:si>
     <x:t>Name</x:t>
   </x:si>
@@ -49,6 +49,9 @@
     <x:t>IsAccredited</x:t>
   </x:si>
   <x:si>
+    <x:t>ContactPerson</x:t>
+  </x:si>
+  <x:si>
     <x:t>cy new employer</x:t>
   </x:si>
   <x:si>
@@ -82,6 +85,9 @@
     <x:t>Accredited</x:t>
   </x:si>
   <x:si>
+    <x:t>nabeel</x:t>
+  </x:si>
+  <x:si>
     <x:t>nimal</x:t>
   </x:si>
   <x:si>
@@ -137,6 +143,9 @@
   </x:si>
   <x:si>
     <x:t>2332</x:t>
+  </x:si>
+  <x:si>
+    <x:t>nabeel ahmed</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -200,9 +209,9 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Grid" displayName="Grid" ref="A1:K10" totalsRowShown="0">
-  <x:autoFilter ref="A1:K10"/>
-  <x:tableColumns count="11">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Grid" displayName="Grid" ref="A1:L10" totalsRowShown="0">
+  <x:autoFilter ref="A1:L10"/>
+  <x:tableColumns count="12">
     <x:tableColumn id="1" name="Name"/>
     <x:tableColumn id="2" name="Email"/>
     <x:tableColumn id="3" name="ContactNo"/>
@@ -214,6 +223,7 @@
     <x:tableColumn id="9" name="EmployerType"/>
     <x:tableColumn id="10" name="IsPotential"/>
     <x:tableColumn id="11" name="IsAccredited"/>
+    <x:tableColumn id="12" name="ContactPerson"/>
   </x:tableColumns>
   <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </x:table>
@@ -507,10 +517,10 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:K10"/>
+  <x:dimension ref="A1:L10"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
-    <x:row r="1" spans="1:11">
+    <x:row r="1" spans="1:12">
       <x:c r="A1" s="0" t="s">
         <x:v>0</x:v>
       </x:c>
@@ -544,185 +554,194 @@
       <x:c r="K1" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
-    </x:row>
-    <x:row r="2" spans="1:11">
+      <x:c r="L1" s="0" t="s">
+        <x:v>11</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="2" spans="1:12">
       <x:c r="A2" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="B2" s="0" t="s">
-        <x:v>12</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="C2" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="D2" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="E2" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="F2" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="G2" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="H2" s="0" t="s">
-        <x:v>18</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="I2" s="0" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="J2" s="0" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="K2" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="L2" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="3" spans="1:12">
+      <x:c r="A3" s="0" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="I3" s="0" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="J3" s="0" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="K3" s="0" t="s">
+        <x:v>25</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="4" spans="1:12">
+      <x:c r="A4" s="0" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="I4" s="0" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="J4" s="0" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="K4" s="0" t="s">
+        <x:v>25</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5" spans="1:12">
+      <x:c r="A5" s="0" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="I5" s="0" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="J5" s="0" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="K5" s="0" t="s">
+        <x:v>25</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6" spans="1:12">
+      <x:c r="A6" s="0" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="I6" s="0" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="J6" s="0" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="K6" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7" spans="1:12">
+      <x:c r="A7" s="0" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="I7" s="0" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="J7" s="0" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="K7" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8" spans="1:12">
+      <x:c r="A8" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="I8" s="0" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="J8" s="0" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="K8" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" spans="1:12">
+      <x:c r="A9" s="0" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="B9" s="0" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="D9" s="0" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="F9" s="0" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="G9" s="0" t="s">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="H9" s="0" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="I9" s="0" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="J9" s="0" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="K9" s="0" t="s">
+        <x:v>25</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" spans="1:12">
+      <x:c r="A10" s="0" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="B10" s="0" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="C10" s="0" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="D10" s="0" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="E10" s="0" t="s">
         <x:v>19</x:v>
       </x:c>
-      <x:c r="J2" s="0" t="s">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="K2" s="0" t="s">
-        <x:v>21</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="3" spans="1:11">
-      <x:c r="A3" s="0" t="s">
+      <x:c r="G10" s="0" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="H10" s="0" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="I10" s="0" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="J10" s="0" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="K10" s="0" t="s">
         <x:v>22</x:v>
       </x:c>
-      <x:c r="I3" s="0" t="s">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c r="J3" s="0" t="s">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="K3" s="0" t="s">
-        <x:v>23</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="4" spans="1:11">
-      <x:c r="A4" s="0" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="I4" s="0" t="s">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c r="J4" s="0" t="s">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="K4" s="0" t="s">
-        <x:v>23</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="5" spans="1:11">
-      <x:c r="A5" s="0" t="s">
-        <x:v>25</x:v>
-      </x:c>
-      <x:c r="I5" s="0" t="s">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c r="J5" s="0" t="s">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="K5" s="0" t="s">
-        <x:v>23</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="6" spans="1:11">
-      <x:c r="A6" s="0" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="I6" s="0" t="s">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c r="J6" s="0" t="s">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="K6" s="0" t="s">
-        <x:v>21</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="7" spans="1:11">
-      <x:c r="A7" s="0" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="I7" s="0" t="s">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c r="J7" s="0" t="s">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="K7" s="0" t="s">
-        <x:v>21</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="8" spans="1:11">
-      <x:c r="A8" s="0" t="s">
-        <x:v>28</x:v>
-      </x:c>
-      <x:c r="I8" s="0" t="s">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c r="J8" s="0" t="s">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="K8" s="0" t="s">
-        <x:v>21</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="9" spans="1:11">
-      <x:c r="A9" s="0" t="s">
-        <x:v>29</x:v>
-      </x:c>
-      <x:c r="B9" s="0" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="D9" s="0" t="s">
-        <x:v>31</x:v>
-      </x:c>
-      <x:c r="F9" s="0" t="s">
-        <x:v>32</x:v>
-      </x:c>
-      <x:c r="G9" s="0" t="s">
-        <x:v>33</x:v>
-      </x:c>
-      <x:c r="H9" s="0" t="s">
-        <x:v>34</x:v>
-      </x:c>
-      <x:c r="I9" s="0" t="s">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c r="J9" s="0" t="s">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="K9" s="0" t="s">
-        <x:v>23</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="10" spans="1:11">
-      <x:c r="A10" s="0" t="s">
-        <x:v>35</x:v>
-      </x:c>
-      <x:c r="B10" s="0" t="s">
-        <x:v>36</x:v>
-      </x:c>
-      <x:c r="C10" s="0" t="s">
-        <x:v>37</x:v>
-      </x:c>
-      <x:c r="D10" s="0" t="s">
-        <x:v>38</x:v>
-      </x:c>
-      <x:c r="E10" s="0" t="s">
-        <x:v>18</x:v>
-      </x:c>
-      <x:c r="G10" s="0" t="s">
-        <x:v>39</x:v>
-      </x:c>
-      <x:c r="H10" s="0" t="s">
-        <x:v>40</x:v>
-      </x:c>
-      <x:c r="I10" s="0" t="s">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c r="J10" s="0" t="s">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="K10" s="0" t="s">
-        <x:v>21</x:v>
+      <x:c r="L10" s="0" t="s">
+        <x:v>43</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/cypress/downloads/EmployersList.xlsx
+++ b/cypress/downloads/EmployersList.xlsx
@@ -91,10 +91,10 @@
     <x:t>nimal</x:t>
   </x:si>
   <x:si>
+    <x:t>employer</x:t>
+  </x:si>
+  <x:si>
     <x:t>N/A</x:t>
-  </x:si>
-  <x:si>
-    <x:t>employer</x:t>
   </x:si>
   <x:si>
     <x:t>lets see</x:t>
@@ -607,21 +607,21 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="K3" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:12">
       <x:c r="A4" s="0" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="I4" s="0" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="J4" s="0" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="K4" s="0" t="s">
         <x:v>26</x:v>
-      </x:c>
-      <x:c r="I4" s="0" t="s">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="J4" s="0" t="s">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="K4" s="0" t="s">
-        <x:v>25</x:v>
       </x:c>
     </x:row>
     <x:row r="5" spans="1:12">
@@ -635,7 +635,7 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="K5" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>26</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:12">
@@ -706,7 +706,7 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="K9" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>26</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:12">

--- a/cypress/downloads/EmployersList.xlsx
+++ b/cypress/downloads/EmployersList.xlsx
@@ -154,7 +154,7 @@
     <x:t>0064211267313</x:t>
   </x:si>
   <x:si>
-    <x:t>outnz</x:t>
+    <x:t>outnz source</x:t>
   </x:si>
   <x:si>
     <x:t>AgricultureFarming</x:t>
@@ -227,8 +227,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Grid" displayName="Grid" ref="A1:L12" totalsRowShown="0">
-  <x:autoFilter ref="A1:L12"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Grid" displayName="Grid" ref="A1:L13" totalsRowShown="0">
+  <x:autoFilter ref="A1:L13"/>
   <x:tableColumns count="12">
     <x:tableColumn id="1" name="Name"/>
     <x:tableColumn id="2" name="Email"/>
@@ -535,7 +535,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:L12"/>
+  <x:dimension ref="A1:L13"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
     <x:row r="1" spans="1:12">
@@ -616,30 +616,51 @@
     </x:row>
     <x:row r="3" spans="1:12">
       <x:c r="A3" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="B3" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="C3" s="0" t="s">
+        <x:v>14</x:v>
       </x:c>
       <x:c r="D3" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="E3" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="F3" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="G3" s="0" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="H3" s="0" t="s">
+        <x:v>19</x:v>
       </x:c>
       <x:c r="I3" s="0" t="s">
         <x:v>20</x:v>
       </x:c>
       <x:c r="J3" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="K3" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="L3" s="0" t="s">
+        <x:v>23</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:12">
       <x:c r="A4" s="0" t="s">
-        <x:v>29</x:v>
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="B4" s="0" t="s">
+        <x:v>25</x:v>
       </x:c>
       <x:c r="D4" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="I4" s="0" t="s">
         <x:v>20</x:v>
@@ -653,21 +674,24 @@
     </x:row>
     <x:row r="5" spans="1:12">
       <x:c r="A5" s="0" t="s">
-        <x:v>31</x:v>
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="D5" s="0" t="s">
+        <x:v>30</x:v>
       </x:c>
       <x:c r="I5" s="0" t="s">
         <x:v>20</x:v>
       </x:c>
       <x:c r="J5" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="K5" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>28</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:12">
       <x:c r="A6" s="0" t="s">
-        <x:v>32</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="I6" s="0" t="s">
         <x:v>20</x:v>
@@ -676,12 +700,12 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="K6" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:12">
       <x:c r="A7" s="0" t="s">
-        <x:v>33</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="I7" s="0" t="s">
         <x:v>20</x:v>
@@ -695,7 +719,7 @@
     </x:row>
     <x:row r="8" spans="1:12">
       <x:c r="A8" s="0" t="s">
-        <x:v>34</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="I8" s="0" t="s">
         <x:v>20</x:v>
@@ -704,12 +728,12 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="K8" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>28</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:12">
       <x:c r="A9" s="0" t="s">
-        <x:v>35</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="I9" s="0" t="s">
         <x:v>20</x:v>
@@ -723,7 +747,7 @@
     </x:row>
     <x:row r="10" spans="1:12">
       <x:c r="A10" s="0" t="s">
-        <x:v>36</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="I10" s="0" t="s">
         <x:v>20</x:v>
@@ -737,22 +761,7 @@
     </x:row>
     <x:row r="11" spans="1:12">
       <x:c r="A11" s="0" t="s">
-        <x:v>37</x:v>
-      </x:c>
-      <x:c r="B11" s="0" t="s">
-        <x:v>38</x:v>
-      </x:c>
-      <x:c r="D11" s="0" t="s">
-        <x:v>39</x:v>
-      </x:c>
-      <x:c r="F11" s="0" t="s">
-        <x:v>40</x:v>
-      </x:c>
-      <x:c r="G11" s="0" t="s">
-        <x:v>41</x:v>
-      </x:c>
-      <x:c r="H11" s="0" t="s">
-        <x:v>42</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="I11" s="0" t="s">
         <x:v>20</x:v>
@@ -761,41 +770,70 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="K11" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:12">
       <x:c r="A12" s="0" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="B12" s="0" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="D12" s="0" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="F12" s="0" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="G12" s="0" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="H12" s="0" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="I12" s="0" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="J12" s="0" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="K12" s="0" t="s">
+        <x:v>28</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13" spans="1:12">
+      <x:c r="A13" s="0" t="s">
         <x:v>43</x:v>
       </x:c>
-      <x:c r="B12" s="0" t="s">
+      <x:c r="B13" s="0" t="s">
         <x:v>44</x:v>
       </x:c>
-      <x:c r="C12" s="0" t="s">
+      <x:c r="C13" s="0" t="s">
         <x:v>45</x:v>
       </x:c>
-      <x:c r="D12" s="0" t="s">
+      <x:c r="D13" s="0" t="s">
         <x:v>46</x:v>
       </x:c>
-      <x:c r="E12" s="0" t="s">
+      <x:c r="E13" s="0" t="s">
         <x:v>19</x:v>
       </x:c>
-      <x:c r="G12" s="0" t="s">
+      <x:c r="G13" s="0" t="s">
         <x:v>47</x:v>
       </x:c>
-      <x:c r="H12" s="0" t="s">
+      <x:c r="H13" s="0" t="s">
         <x:v>48</x:v>
       </x:c>
-      <x:c r="I12" s="0" t="s">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="J12" s="0" t="s">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="K12" s="0" t="s">
+      <x:c r="I13" s="0" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="J13" s="0" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="K13" s="0" t="s">
         <x:v>22</x:v>
       </x:c>
-      <x:c r="L12" s="0" t="s">
+      <x:c r="L13" s="0" t="s">
         <x:v>49</x:v>
       </x:c>
     </x:row>

--- a/cypress/downloads/EmployersList.xlsx
+++ b/cypress/downloads/EmployersList.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="50">
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="51">
   <x:si>
     <x:t>Name</x:t>
   </x:si>
@@ -52,6 +52,9 @@
     <x:t>Contact Person</x:t>
   </x:si>
   <x:si>
+    <x:t>Processing Person</x:t>
+  </x:si>
+  <x:si>
     <x:t>cy new employer</x:t>
   </x:si>
   <x:si>
@@ -88,21 +91,21 @@
     <x:t>nabeel</x:t>
   </x:si>
   <x:si>
+    <x:t>test</x:t>
+  </x:si>
+  <x:si>
+    <x:t>N/A</x:t>
+  </x:si>
+  <x:si>
     <x:t>milt</x:t>
   </x:si>
   <x:si>
     <x:t>test@gmail.com</x:t>
   </x:si>
   <x:si>
-    <x:t>test</x:t>
-  </x:si>
-  <x:si>
     <x:t>Yes</x:t>
   </x:si>
   <x:si>
-    <x:t>N/A</x:t>
-  </x:si>
-  <x:si>
     <x:t>tsest</x:t>
   </x:si>
   <x:si>
@@ -112,19 +115,19 @@
     <x:t>nimal</x:t>
   </x:si>
   <x:si>
+    <x:t>Owner nabeel</x:t>
+  </x:si>
+  <x:si>
     <x:t>employer</x:t>
   </x:si>
   <x:si>
-    <x:t>lets see</x:t>
-  </x:si>
-  <x:si>
     <x:t>mlian</x:t>
   </x:si>
   <x:si>
-    <x:t>test123</x:t>
-  </x:si>
-  <x:si>
     <x:t>test new em</x:t>
+  </x:si>
+  <x:si>
+    <x:t>arsalan team member</x:t>
   </x:si>
   <x:si>
     <x:t>recruiter emp</x:t>
@@ -227,9 +230,9 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Grid" displayName="Grid" ref="A1:L13" totalsRowShown="0">
-  <x:autoFilter ref="A1:L13"/>
-  <x:tableColumns count="12">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Grid" displayName="Grid" ref="A1:M11" totalsRowShown="0">
+  <x:autoFilter ref="A1:M11"/>
+  <x:tableColumns count="13">
     <x:tableColumn id="1" name="Name"/>
     <x:tableColumn id="2" name="Email"/>
     <x:tableColumn id="3" name="ContactNo"/>
@@ -242,6 +245,7 @@
     <x:tableColumn id="10" name="IsPotential"/>
     <x:tableColumn id="11" name="IsAccredited"/>
     <x:tableColumn id="12" name="Contact Person"/>
+    <x:tableColumn id="13" name="Processing Person"/>
   </x:tableColumns>
   <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </x:table>
@@ -535,10 +539,10 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:L13"/>
+  <x:dimension ref="A1:M11"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
-    <x:row r="1" spans="1:12">
+    <x:row r="1" spans="1:13">
       <x:c r="A1" s="0" t="s">
         <x:v>0</x:v>
       </x:c>
@@ -575,266 +579,226 @@
       <x:c r="L1" s="0" t="s">
         <x:v>11</x:v>
       </x:c>
-    </x:row>
-    <x:row r="2" spans="1:12">
+      <x:c r="M1" s="0" t="s">
+        <x:v>12</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="2" spans="1:13">
       <x:c r="A2" s="0" t="s">
-        <x:v>12</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="B2" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C2" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="D2" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="E2" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="F2" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="G2" s="0" t="s">
-        <x:v>18</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="H2" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="I2" s="0" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="J2" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="K2" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="L2" s="0" t="s">
+        <x:v>24</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="3" spans="1:13">
+      <x:c r="A3" s="0" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="I3" s="0" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="J3" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="K3" s="0" t="s">
+        <x:v>26</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="4" spans="1:13">
+      <x:c r="A4" s="0" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="B4" s="0" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="D4" s="0" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="I4" s="0" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="J4" s="0" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="K4" s="0" t="s">
+        <x:v>26</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5" spans="1:13">
+      <x:c r="A5" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="D5" s="0" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="I5" s="0" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="J5" s="0" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="K5" s="0" t="s">
+        <x:v>26</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6" spans="1:13">
+      <x:c r="A6" s="0" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="I6" s="0" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="J6" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="K6" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="M6" s="0" t="s">
+        <x:v>33</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7" spans="1:13">
+      <x:c r="A7" s="0" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="I7" s="0" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="J7" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="K7" s="0" t="s">
+        <x:v>26</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8" spans="1:13">
+      <x:c r="A8" s="0" t="s">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="I8" s="0" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="J8" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="K8" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" spans="1:13">
+      <x:c r="A9" s="0" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="I9" s="0" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="J9" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="K9" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="M9" s="0" t="s">
+        <x:v>37</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" spans="1:13">
+      <x:c r="A10" s="0" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="B10" s="0" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="D10" s="0" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="F10" s="0" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="G10" s="0" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="H10" s="0" t="s">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="I10" s="0" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="J10" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="K10" s="0" t="s">
+        <x:v>26</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" spans="1:13">
+      <x:c r="A11" s="0" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="B11" s="0" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="C11" s="0" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="D11" s="0" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="E11" s="0" t="s">
         <x:v>20</x:v>
       </x:c>
-      <x:c r="J2" s="0" t="s">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="K2" s="0" t="s">
+      <x:c r="G11" s="0" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="H11" s="0" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="I11" s="0" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="J11" s="0" t="s">
         <x:v>22</x:v>
       </x:c>
-      <x:c r="L2" s="0" t="s">
+      <x:c r="K11" s="0" t="s">
         <x:v>23</x:v>
       </x:c>
-    </x:row>
-    <x:row r="3" spans="1:12">
-      <x:c r="A3" s="0" t="s">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="B3" s="0" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="C3" s="0" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="D3" s="0" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="E3" s="0" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="F3" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="G3" s="0" t="s">
-        <x:v>18</x:v>
-      </x:c>
-      <x:c r="H3" s="0" t="s">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c r="I3" s="0" t="s">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="J3" s="0" t="s">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="K3" s="0" t="s">
-        <x:v>22</x:v>
-      </x:c>
-      <x:c r="L3" s="0" t="s">
-        <x:v>23</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="4" spans="1:12">
-      <x:c r="A4" s="0" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="B4" s="0" t="s">
-        <x:v>25</x:v>
-      </x:c>
-      <x:c r="D4" s="0" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="I4" s="0" t="s">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="J4" s="0" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="K4" s="0" t="s">
-        <x:v>28</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="5" spans="1:12">
-      <x:c r="A5" s="0" t="s">
-        <x:v>29</x:v>
-      </x:c>
-      <x:c r="D5" s="0" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="I5" s="0" t="s">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="J5" s="0" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="K5" s="0" t="s">
-        <x:v>28</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="6" spans="1:12">
-      <x:c r="A6" s="0" t="s">
-        <x:v>31</x:v>
-      </x:c>
-      <x:c r="I6" s="0" t="s">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="J6" s="0" t="s">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="K6" s="0" t="s">
-        <x:v>22</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="7" spans="1:12">
-      <x:c r="A7" s="0" t="s">
-        <x:v>32</x:v>
-      </x:c>
-      <x:c r="I7" s="0" t="s">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="J7" s="0" t="s">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="K7" s="0" t="s">
-        <x:v>28</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="8" spans="1:12">
-      <x:c r="A8" s="0" t="s">
+      <x:c r="L11" s="0" t="s">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="M11" s="0" t="s">
         <x:v>33</x:v>
-      </x:c>
-      <x:c r="I8" s="0" t="s">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="J8" s="0" t="s">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="K8" s="0" t="s">
-        <x:v>28</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="9" spans="1:12">
-      <x:c r="A9" s="0" t="s">
-        <x:v>34</x:v>
-      </x:c>
-      <x:c r="I9" s="0" t="s">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="J9" s="0" t="s">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="K9" s="0" t="s">
-        <x:v>22</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="10" spans="1:12">
-      <x:c r="A10" s="0" t="s">
-        <x:v>35</x:v>
-      </x:c>
-      <x:c r="I10" s="0" t="s">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="J10" s="0" t="s">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="K10" s="0" t="s">
-        <x:v>22</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="11" spans="1:12">
-      <x:c r="A11" s="0" t="s">
-        <x:v>36</x:v>
-      </x:c>
-      <x:c r="I11" s="0" t="s">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="J11" s="0" t="s">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="K11" s="0" t="s">
-        <x:v>22</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="12" spans="1:12">
-      <x:c r="A12" s="0" t="s">
-        <x:v>37</x:v>
-      </x:c>
-      <x:c r="B12" s="0" t="s">
-        <x:v>38</x:v>
-      </x:c>
-      <x:c r="D12" s="0" t="s">
-        <x:v>39</x:v>
-      </x:c>
-      <x:c r="F12" s="0" t="s">
-        <x:v>40</x:v>
-      </x:c>
-      <x:c r="G12" s="0" t="s">
-        <x:v>41</x:v>
-      </x:c>
-      <x:c r="H12" s="0" t="s">
-        <x:v>42</x:v>
-      </x:c>
-      <x:c r="I12" s="0" t="s">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="J12" s="0" t="s">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="K12" s="0" t="s">
-        <x:v>28</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="13" spans="1:12">
-      <x:c r="A13" s="0" t="s">
-        <x:v>43</x:v>
-      </x:c>
-      <x:c r="B13" s="0" t="s">
-        <x:v>44</x:v>
-      </x:c>
-      <x:c r="C13" s="0" t="s">
-        <x:v>45</x:v>
-      </x:c>
-      <x:c r="D13" s="0" t="s">
-        <x:v>46</x:v>
-      </x:c>
-      <x:c r="E13" s="0" t="s">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c r="G13" s="0" t="s">
-        <x:v>47</x:v>
-      </x:c>
-      <x:c r="H13" s="0" t="s">
-        <x:v>48</x:v>
-      </x:c>
-      <x:c r="I13" s="0" t="s">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="J13" s="0" t="s">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="K13" s="0" t="s">
-        <x:v>22</x:v>
-      </x:c>
-      <x:c r="L13" s="0" t="s">
-        <x:v>49</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/cypress/downloads/EmployersList.xlsx
+++ b/cypress/downloads/EmployersList.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="51">
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="53">
   <x:si>
     <x:t>Name</x:t>
   </x:si>
@@ -49,12 +49,18 @@
     <x:t>IsAccredited</x:t>
   </x:si>
   <x:si>
+    <x:t>Accredation Expiry Date</x:t>
+  </x:si>
+  <x:si>
     <x:t>Contact Person</x:t>
   </x:si>
   <x:si>
     <x:t>Processing Person</x:t>
   </x:si>
   <x:si>
+    <x:t>Tags</x:t>
+  </x:si>
+  <x:si>
     <x:t>cy new employer</x:t>
   </x:si>
   <x:si>
@@ -88,6 +94,9 @@
     <x:t>Accredited</x:t>
   </x:si>
   <x:si>
+    <x:t>24/12/2023</x:t>
+  </x:si>
+  <x:si>
     <x:t>nabeel</x:t>
   </x:si>
   <x:si>
@@ -112,61 +121,58 @@
     <x:t>rwar</x:t>
   </x:si>
   <x:si>
-    <x:t>nimal</x:t>
+    <x:t>employer</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">tag 3 </x:t>
+  </x:si>
+  <x:si>
+    <x:t>mlian</x:t>
+  </x:si>
+  <x:si>
+    <x:t>27/02/2023</x:t>
+  </x:si>
+  <x:si>
+    <x:t>test new em</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26/01/2023</x:t>
+  </x:si>
+  <x:si>
+    <x:t>arsalan team member</x:t>
+  </x:si>
+  <x:si>
+    <x:t>tag 3 ,tag 2</x:t>
+  </x:si>
+  <x:si>
+    <x:t>supplier emp</x:t>
+  </x:si>
+  <x:si>
+    <x:t>rananabeelahmed772@gmail.com</x:t>
+  </x:si>
+  <x:si>
+    <x:t>0064211267313</x:t>
+  </x:si>
+  <x:si>
+    <x:t>outnz source</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AgricultureFarming</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2332</x:t>
+  </x:si>
+  <x:si>
+    <x:t>24/02/2023</x:t>
+  </x:si>
+  <x:si>
+    <x:t>nabeel ahmed</x:t>
   </x:si>
   <x:si>
     <x:t>Owner nabeel</x:t>
   </x:si>
   <x:si>
-    <x:t>employer</x:t>
-  </x:si>
-  <x:si>
-    <x:t>mlian</x:t>
-  </x:si>
-  <x:si>
-    <x:t>test new em</x:t>
-  </x:si>
-  <x:si>
-    <x:t>arsalan team member</x:t>
-  </x:si>
-  <x:si>
-    <x:t>recruiter emp</x:t>
-  </x:si>
-  <x:si>
-    <x:t>nabeeloutsourcenz1@gmail.com</x:t>
-  </x:si>
-  <x:si>
-    <x:t>out</x:t>
-  </x:si>
-  <x:si>
-    <x:t>+64211267313</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Engineer</x:t>
-  </x:si>
-  <x:si>
-    <x:t>323</x:t>
-  </x:si>
-  <x:si>
-    <x:t>supplier emp</x:t>
-  </x:si>
-  <x:si>
-    <x:t>rananabeelahmed772@gmail.com</x:t>
-  </x:si>
-  <x:si>
-    <x:t>0064211267313</x:t>
-  </x:si>
-  <x:si>
-    <x:t>outnz source</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AgricultureFarming</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2332</x:t>
-  </x:si>
-  <x:si>
-    <x:t>nabeel ahmed</x:t>
+    <x:t>tag 2</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -230,9 +236,9 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Grid" displayName="Grid" ref="A1:M11" totalsRowShown="0">
-  <x:autoFilter ref="A1:M11"/>
-  <x:tableColumns count="13">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Grid" displayName="Grid" ref="A1:O9" totalsRowShown="0">
+  <x:autoFilter ref="A1:O9"/>
+  <x:tableColumns count="15">
     <x:tableColumn id="1" name="Name"/>
     <x:tableColumn id="2" name="Email"/>
     <x:tableColumn id="3" name="ContactNo"/>
@@ -244,8 +250,10 @@
     <x:tableColumn id="9" name="EmployerType"/>
     <x:tableColumn id="10" name="IsPotential"/>
     <x:tableColumn id="11" name="IsAccredited"/>
-    <x:tableColumn id="12" name="Contact Person"/>
-    <x:tableColumn id="13" name="Processing Person"/>
+    <x:tableColumn id="12" name="Accredation Expiry Date"/>
+    <x:tableColumn id="13" name="Contact Person"/>
+    <x:tableColumn id="14" name="Processing Person"/>
+    <x:tableColumn id="15" name="Tags"/>
   </x:tableColumns>
   <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </x:table>
@@ -539,10 +547,10 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:M11"/>
+  <x:dimension ref="A1:O9"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
-    <x:row r="1" spans="1:13">
+    <x:row r="1" spans="1:15">
       <x:c r="A1" s="0" t="s">
         <x:v>0</x:v>
       </x:c>
@@ -582,223 +590,204 @@
       <x:c r="M1" s="0" t="s">
         <x:v>12</x:v>
       </x:c>
+      <x:c r="N1" s="0" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="O1" s="0" t="s">
+        <x:v>14</x:v>
+      </x:c>
     </x:row>
-    <x:row r="2" spans="1:13">
+    <x:row r="2" spans="1:15">
       <x:c r="A2" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="B2" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="C2" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="D2" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="E2" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="F2" s="0" t="s">
-        <x:v>18</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="G2" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="H2" s="0" t="s">
-        <x:v>20</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="I2" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="J2" s="0" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="K2" s="0" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="L2" s="0" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="M2" s="0" t="s">
+        <x:v>27</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="3" spans="1:15">
+      <x:c r="A3" s="0" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="I3" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="J3" s="0" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="K3" s="0" t="s">
+        <x:v>29</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="4" spans="1:15">
+      <x:c r="A4" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="B4" s="0" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="D4" s="0" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="I4" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="J4" s="0" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="K4" s="0" t="s">
+        <x:v>29</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5" spans="1:15">
+      <x:c r="A5" s="0" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="D5" s="0" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="I5" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="J5" s="0" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="K5" s="0" t="s">
+        <x:v>29</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6" spans="1:15">
+      <x:c r="A6" s="0" t="s">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="I6" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="J6" s="0" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="K6" s="0" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="O6" s="0" t="s">
+        <x:v>36</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7" spans="1:15">
+      <x:c r="A7" s="0" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="I7" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="J7" s="0" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="K7" s="0" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="L7" s="0" t="s">
+        <x:v>38</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8" spans="1:15">
+      <x:c r="A8" s="0" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="I8" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="J8" s="0" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="K8" s="0" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="L8" s="0" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="N8" s="0" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="O8" s="0" t="s">
+        <x:v>42</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" spans="1:15">
+      <x:c r="A9" s="0" t="s">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="B9" s="0" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="C9" s="0" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="D9" s="0" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="E9" s="0" t="s">
         <x:v>22</x:v>
       </x:c>
-      <x:c r="K2" s="0" t="s">
+      <x:c r="G9" s="0" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="H9" s="0" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="I9" s="0" t="s">
         <x:v>23</x:v>
       </x:c>
-      <x:c r="L2" s="0" t="s">
+      <x:c r="J9" s="0" t="s">
         <x:v>24</x:v>
       </x:c>
-    </x:row>
-    <x:row r="3" spans="1:13">
-      <x:c r="A3" s="0" t="s">
+      <x:c r="K9" s="0" t="s">
         <x:v>25</x:v>
       </x:c>
-      <x:c r="I3" s="0" t="s">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="J3" s="0" t="s">
-        <x:v>22</x:v>
-      </x:c>
-      <x:c r="K3" s="0" t="s">
-        <x:v>26</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="4" spans="1:13">
-      <x:c r="A4" s="0" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="B4" s="0" t="s">
-        <x:v>28</x:v>
-      </x:c>
-      <x:c r="D4" s="0" t="s">
-        <x:v>25</x:v>
-      </x:c>
-      <x:c r="I4" s="0" t="s">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="J4" s="0" t="s">
-        <x:v>29</x:v>
-      </x:c>
-      <x:c r="K4" s="0" t="s">
-        <x:v>26</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="5" spans="1:13">
-      <x:c r="A5" s="0" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="D5" s="0" t="s">
-        <x:v>31</x:v>
-      </x:c>
-      <x:c r="I5" s="0" t="s">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="J5" s="0" t="s">
-        <x:v>29</x:v>
-      </x:c>
-      <x:c r="K5" s="0" t="s">
-        <x:v>26</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="6" spans="1:13">
-      <x:c r="A6" s="0" t="s">
-        <x:v>32</x:v>
-      </x:c>
-      <x:c r="I6" s="0" t="s">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="J6" s="0" t="s">
-        <x:v>22</x:v>
-      </x:c>
-      <x:c r="K6" s="0" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="M6" s="0" t="s">
-        <x:v>33</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="7" spans="1:13">
-      <x:c r="A7" s="0" t="s">
-        <x:v>34</x:v>
-      </x:c>
-      <x:c r="I7" s="0" t="s">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="J7" s="0" t="s">
-        <x:v>22</x:v>
-      </x:c>
-      <x:c r="K7" s="0" t="s">
-        <x:v>26</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="8" spans="1:13">
-      <x:c r="A8" s="0" t="s">
-        <x:v>35</x:v>
-      </x:c>
-      <x:c r="I8" s="0" t="s">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="J8" s="0" t="s">
-        <x:v>22</x:v>
-      </x:c>
-      <x:c r="K8" s="0" t="s">
-        <x:v>23</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="9" spans="1:13">
-      <x:c r="A9" s="0" t="s">
-        <x:v>36</x:v>
-      </x:c>
-      <x:c r="I9" s="0" t="s">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="J9" s="0" t="s">
-        <x:v>22</x:v>
-      </x:c>
-      <x:c r="K9" s="0" t="s">
-        <x:v>23</x:v>
+      <x:c r="L9" s="0" t="s">
+        <x:v>49</x:v>
       </x:c>
       <x:c r="M9" s="0" t="s">
-        <x:v>37</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="10" spans="1:13">
-      <x:c r="A10" s="0" t="s">
-        <x:v>38</x:v>
-      </x:c>
-      <x:c r="B10" s="0" t="s">
-        <x:v>39</x:v>
-      </x:c>
-      <x:c r="D10" s="0" t="s">
-        <x:v>40</x:v>
-      </x:c>
-      <x:c r="F10" s="0" t="s">
-        <x:v>41</x:v>
-      </x:c>
-      <x:c r="G10" s="0" t="s">
-        <x:v>42</x:v>
-      </x:c>
-      <x:c r="H10" s="0" t="s">
-        <x:v>43</x:v>
-      </x:c>
-      <x:c r="I10" s="0" t="s">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="J10" s="0" t="s">
-        <x:v>22</x:v>
-      </x:c>
-      <x:c r="K10" s="0" t="s">
-        <x:v>26</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="11" spans="1:13">
-      <x:c r="A11" s="0" t="s">
-        <x:v>44</x:v>
-      </x:c>
-      <x:c r="B11" s="0" t="s">
-        <x:v>45</x:v>
-      </x:c>
-      <x:c r="C11" s="0" t="s">
-        <x:v>46</x:v>
-      </x:c>
-      <x:c r="D11" s="0" t="s">
-        <x:v>47</x:v>
-      </x:c>
-      <x:c r="E11" s="0" t="s">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="G11" s="0" t="s">
-        <x:v>48</x:v>
-      </x:c>
-      <x:c r="H11" s="0" t="s">
-        <x:v>49</x:v>
-      </x:c>
-      <x:c r="I11" s="0" t="s">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="J11" s="0" t="s">
-        <x:v>22</x:v>
-      </x:c>
-      <x:c r="K11" s="0" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="L11" s="0" t="s">
         <x:v>50</x:v>
       </x:c>
-      <x:c r="M11" s="0" t="s">
-        <x:v>33</x:v>
+      <x:c r="N9" s="0" t="s">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="O9" s="0" t="s">
+        <x:v>52</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/cypress/downloads/EmployersList.xlsx
+++ b/cypress/downloads/EmployersList.xlsx
@@ -100,19 +100,19 @@
     <x:t>nabeel</x:t>
   </x:si>
   <x:si>
+    <x:t>milt</x:t>
+  </x:si>
+  <x:si>
+    <x:t>test@gmail.com</x:t>
+  </x:si>
+  <x:si>
     <x:t>test</x:t>
   </x:si>
   <x:si>
+    <x:t>Yes</x:t>
+  </x:si>
+  <x:si>
     <x:t>N/A</x:t>
-  </x:si>
-  <x:si>
-    <x:t>milt</x:t>
-  </x:si>
-  <x:si>
-    <x:t>test@gmail.com</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Yes</x:t>
   </x:si>
   <x:si>
     <x:t>tsest</x:t>
@@ -236,8 +236,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Grid" displayName="Grid" ref="A1:O9" totalsRowShown="0">
-  <x:autoFilter ref="A1:O9"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Grid" displayName="Grid" ref="A1:O8" totalsRowShown="0">
+  <x:autoFilter ref="A1:O8"/>
   <x:tableColumns count="15">
     <x:tableColumn id="1" name="Name"/>
     <x:tableColumn id="2" name="Email"/>
@@ -547,7 +547,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:O9"/>
+  <x:dimension ref="A1:O8"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
     <x:row r="1" spans="1:15">
@@ -642,56 +642,59 @@
       <x:c r="A3" s="0" t="s">
         <x:v>28</x:v>
       </x:c>
+      <x:c r="B3" s="0" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="D3" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
       <x:c r="I3" s="0" t="s">
         <x:v>23</x:v>
       </x:c>
       <x:c r="J3" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="K3" s="0" t="s">
-        <x:v>29</x:v>
+        <x:v>32</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:15">
       <x:c r="A4" s="0" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="B4" s="0" t="s">
-        <x:v>31</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="D4" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="I4" s="0" t="s">
         <x:v>23</x:v>
       </x:c>
       <x:c r="J4" s="0" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="K4" s="0" t="s">
         <x:v>32</x:v>
-      </x:c>
-      <x:c r="K4" s="0" t="s">
-        <x:v>29</x:v>
       </x:c>
     </x:row>
     <x:row r="5" spans="1:15">
       <x:c r="A5" s="0" t="s">
-        <x:v>33</x:v>
-      </x:c>
-      <x:c r="D5" s="0" t="s">
-        <x:v>34</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="I5" s="0" t="s">
         <x:v>23</x:v>
       </x:c>
       <x:c r="J5" s="0" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="K5" s="0" t="s">
         <x:v>32</x:v>
       </x:c>
-      <x:c r="K5" s="0" t="s">
-        <x:v>29</x:v>
+      <x:c r="O5" s="0" t="s">
+        <x:v>36</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:15">
       <x:c r="A6" s="0" t="s">
-        <x:v>35</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="I6" s="0" t="s">
         <x:v>23</x:v>
@@ -700,15 +703,15 @@
         <x:v>24</x:v>
       </x:c>
       <x:c r="K6" s="0" t="s">
-        <x:v>29</x:v>
-      </x:c>
-      <x:c r="O6" s="0" t="s">
-        <x:v>36</x:v>
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="L6" s="0" t="s">
+        <x:v>38</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:15">
       <x:c r="A7" s="0" t="s">
-        <x:v>37</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="I7" s="0" t="s">
         <x:v>23</x:v>
@@ -720,12 +723,36 @@
         <x:v>25</x:v>
       </x:c>
       <x:c r="L7" s="0" t="s">
-        <x:v>38</x:v>
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="N7" s="0" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="O7" s="0" t="s">
+        <x:v>42</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:15">
       <x:c r="A8" s="0" t="s">
-        <x:v>39</x:v>
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="B8" s="0" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="C8" s="0" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="D8" s="0" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="E8" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="G8" s="0" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="H8" s="0" t="s">
+        <x:v>48</x:v>
       </x:c>
       <x:c r="I8" s="0" t="s">
         <x:v>23</x:v>
@@ -737,56 +764,15 @@
         <x:v>25</x:v>
       </x:c>
       <x:c r="L8" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="M8" s="0" t="s">
+        <x:v>50</x:v>
       </x:c>
       <x:c r="N8" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="O8" s="0" t="s">
-        <x:v>42</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="9" spans="1:15">
-      <x:c r="A9" s="0" t="s">
-        <x:v>43</x:v>
-      </x:c>
-      <x:c r="B9" s="0" t="s">
-        <x:v>44</x:v>
-      </x:c>
-      <x:c r="C9" s="0" t="s">
-        <x:v>45</x:v>
-      </x:c>
-      <x:c r="D9" s="0" t="s">
-        <x:v>46</x:v>
-      </x:c>
-      <x:c r="E9" s="0" t="s">
-        <x:v>22</x:v>
-      </x:c>
-      <x:c r="G9" s="0" t="s">
-        <x:v>47</x:v>
-      </x:c>
-      <x:c r="H9" s="0" t="s">
-        <x:v>48</x:v>
-      </x:c>
-      <x:c r="I9" s="0" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="J9" s="0" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="K9" s="0" t="s">
-        <x:v>25</x:v>
-      </x:c>
-      <x:c r="L9" s="0" t="s">
-        <x:v>49</x:v>
-      </x:c>
-      <x:c r="M9" s="0" t="s">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="N9" s="0" t="s">
-        <x:v>51</x:v>
-      </x:c>
-      <x:c r="O9" s="0" t="s">
         <x:v>52</x:v>
       </x:c>
     </x:row>

--- a/cypress/downloads/EmployersList.xlsx
+++ b/cypress/downloads/EmployersList.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="53">
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="72">
   <x:si>
     <x:t>Name</x:t>
   </x:si>
@@ -100,12 +100,75 @@
     <x:t>nabeel</x:t>
   </x:si>
   <x:si>
+    <x:t>new nabeel employer</x:t>
+  </x:si>
+  <x:si>
+    <x:t>test@gmail.com</x:t>
+  </x:si>
+  <x:si>
+    <x:t>+920303031</x:t>
+  </x:si>
+  <x:si>
+    <x:t>company name</x:t>
+  </x:si>
+  <x:si>
+    <x:t>tet ct</x:t>
+  </x:si>
+  <x:si>
+    <x:t>122121212</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Finance</x:t>
+  </x:si>
+  <x:si>
+    <x:t>12</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Supplier</x:t>
+  </x:si>
+  <x:si>
+    <x:t>07/02/2024</x:t>
+  </x:si>
+  <x:si>
+    <x:t>contact us</x:t>
+  </x:si>
+  <x:si>
+    <x:t>tag 1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>microsoft 1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>microsoft@gmail.com</x:t>
+  </x:si>
+  <x:si>
+    <x:t>company name 1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>test city 1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>+221221212211</x:t>
+  </x:si>
+  <x:si>
+    <x:t>121</x:t>
+  </x:si>
+  <x:si>
+    <x:t>14/02/2024</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Nabeel 1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Owner nabeel</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">tag 3 </x:t>
+  </x:si>
+  <x:si>
     <x:t>milt</x:t>
   </x:si>
   <x:si>
-    <x:t>test@gmail.com</x:t>
-  </x:si>
-  <x:si>
     <x:t>test</x:t>
   </x:si>
   <x:si>
@@ -124,9 +187,6 @@
     <x:t>employer</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">tag 3 </x:t>
-  </x:si>
-  <x:si>
     <x:t>mlian</x:t>
   </x:si>
   <x:si>
@@ -167,9 +227,6 @@
   </x:si>
   <x:si>
     <x:t>nabeel ahmed</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Owner nabeel</x:t>
   </x:si>
   <x:si>
     <x:t>tag 2</x:t>
@@ -236,8 +293,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Grid" displayName="Grid" ref="A1:O8" totalsRowShown="0">
-  <x:autoFilter ref="A1:O8"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Grid" displayName="Grid" ref="A1:O10" totalsRowShown="0">
+  <x:autoFilter ref="A1:O10"/>
   <x:tableColumns count="15">
     <x:tableColumn id="1" name="Name"/>
     <x:tableColumn id="2" name="Email"/>
@@ -547,7 +604,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:O8"/>
+  <x:dimension ref="A1:O10"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
     <x:row r="1" spans="1:15">
@@ -645,73 +702,130 @@
       <x:c r="B3" s="0" t="s">
         <x:v>29</x:v>
       </x:c>
+      <x:c r="C3" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
       <x:c r="D3" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="E3" s="0" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="F3" s="0" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="G3" s="0" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="H3" s="0" t="s">
+        <x:v>35</x:v>
       </x:c>
       <x:c r="I3" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="J3" s="0" t="s">
-        <x:v>31</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="K3" s="0" t="s">
-        <x:v>32</x:v>
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="L3" s="0" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="M3" s="0" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="O3" s="0" t="s">
+        <x:v>39</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:15">
       <x:c r="A4" s="0" t="s">
-        <x:v>33</x:v>
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="B4" s="0" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="C4" s="0" t="s">
+        <x:v>30</x:v>
       </x:c>
       <x:c r="D4" s="0" t="s">
-        <x:v>34</x:v>
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="E4" s="0" t="s">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="F4" s="0" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="G4" s="0" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="H4" s="0" t="s">
+        <x:v>45</x:v>
       </x:c>
       <x:c r="I4" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="J4" s="0" t="s">
-        <x:v>31</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="K4" s="0" t="s">
-        <x:v>32</x:v>
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="L4" s="0" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="M4" s="0" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="N4" s="0" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="O4" s="0" t="s">
+        <x:v>49</x:v>
       </x:c>
     </x:row>
     <x:row r="5" spans="1:15">
       <x:c r="A5" s="0" t="s">
-        <x:v>35</x:v>
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="B5" s="0" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="D5" s="0" t="s">
+        <x:v>51</x:v>
       </x:c>
       <x:c r="I5" s="0" t="s">
         <x:v>23</x:v>
       </x:c>
       <x:c r="J5" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="K5" s="0" t="s">
-        <x:v>32</x:v>
-      </x:c>
-      <x:c r="O5" s="0" t="s">
-        <x:v>36</x:v>
+        <x:v>53</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:15">
       <x:c r="A6" s="0" t="s">
-        <x:v>37</x:v>
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="D6" s="0" t="s">
+        <x:v>55</x:v>
       </x:c>
       <x:c r="I6" s="0" t="s">
         <x:v>23</x:v>
       </x:c>
       <x:c r="J6" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="K6" s="0" t="s">
-        <x:v>25</x:v>
-      </x:c>
-      <x:c r="L6" s="0" t="s">
-        <x:v>38</x:v>
+        <x:v>53</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:15">
       <x:c r="A7" s="0" t="s">
-        <x:v>39</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="I7" s="0" t="s">
         <x:v>23</x:v>
@@ -720,39 +834,15 @@
         <x:v>24</x:v>
       </x:c>
       <x:c r="K7" s="0" t="s">
-        <x:v>25</x:v>
-      </x:c>
-      <x:c r="L7" s="0" t="s">
-        <x:v>40</x:v>
-      </x:c>
-      <x:c r="N7" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="O7" s="0" t="s">
-        <x:v>42</x:v>
+        <x:v>49</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:15">
       <x:c r="A8" s="0" t="s">
-        <x:v>43</x:v>
-      </x:c>
-      <x:c r="B8" s="0" t="s">
-        <x:v>44</x:v>
-      </x:c>
-      <x:c r="C8" s="0" t="s">
-        <x:v>45</x:v>
-      </x:c>
-      <x:c r="D8" s="0" t="s">
-        <x:v>46</x:v>
-      </x:c>
-      <x:c r="E8" s="0" t="s">
-        <x:v>22</x:v>
-      </x:c>
-      <x:c r="G8" s="0" t="s">
-        <x:v>47</x:v>
-      </x:c>
-      <x:c r="H8" s="0" t="s">
-        <x:v>48</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="I8" s="0" t="s">
         <x:v>23</x:v>
@@ -764,16 +854,74 @@
         <x:v>25</x:v>
       </x:c>
       <x:c r="L8" s="0" t="s">
-        <x:v>49</x:v>
-      </x:c>
-      <x:c r="M8" s="0" t="s">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="N8" s="0" t="s">
-        <x:v>51</x:v>
-      </x:c>
-      <x:c r="O8" s="0" t="s">
-        <x:v>52</x:v>
+        <x:v>58</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" spans="1:15">
+      <x:c r="A9" s="0" t="s">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="I9" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="J9" s="0" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="K9" s="0" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="L9" s="0" t="s">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="N9" s="0" t="s">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="O9" s="0" t="s">
+        <x:v>62</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" spans="1:15">
+      <x:c r="A10" s="0" t="s">
+        <x:v>63</x:v>
+      </x:c>
+      <x:c r="B10" s="0" t="s">
+        <x:v>64</x:v>
+      </x:c>
+      <x:c r="C10" s="0" t="s">
+        <x:v>65</x:v>
+      </x:c>
+      <x:c r="D10" s="0" t="s">
+        <x:v>66</x:v>
+      </x:c>
+      <x:c r="E10" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="G10" s="0" t="s">
+        <x:v>67</x:v>
+      </x:c>
+      <x:c r="H10" s="0" t="s">
+        <x:v>68</x:v>
+      </x:c>
+      <x:c r="I10" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="J10" s="0" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="K10" s="0" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="L10" s="0" t="s">
+        <x:v>69</x:v>
+      </x:c>
+      <x:c r="M10" s="0" t="s">
+        <x:v>70</x:v>
+      </x:c>
+      <x:c r="N10" s="0" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="O10" s="0" t="s">
+        <x:v>71</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/cypress/downloads/EmployersList.xlsx
+++ b/cypress/downloads/EmployersList.xlsx
@@ -94,7 +94,7 @@
     <x:t>Accredited</x:t>
   </x:si>
   <x:si>
-    <x:t>24/12/2023</x:t>
+    <x:t>24/12/2024</x:t>
   </x:si>
   <x:si>
     <x:t>nabeel</x:t>

--- a/cypress/downloads/EmployersList.xlsx
+++ b/cypress/downloads/EmployersList.xlsx
@@ -133,6 +133,9 @@
     <x:t>contact us</x:t>
   </x:si>
   <x:si>
+    <x:t>Owner nabeel</x:t>
+  </x:si>
+  <x:si>
     <x:t>tag 1</x:t>
   </x:si>
   <x:si>
@@ -158,9 +161,6 @@
   </x:si>
   <x:si>
     <x:t>Nabeel 1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Owner nabeel</x:t>
   </x:si>
   <x:si>
     <x:t xml:space="preserve">tag 3 </x:t>
@@ -735,34 +735,37 @@
       <x:c r="M3" s="0" t="s">
         <x:v>38</x:v>
       </x:c>
+      <x:c r="N3" s="0" t="s">
+        <x:v>39</x:v>
+      </x:c>
       <x:c r="O3" s="0" t="s">
-        <x:v>39</x:v>
+        <x:v>40</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:15">
       <x:c r="A4" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="B4" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="C4" s="0" t="s">
         <x:v>30</x:v>
       </x:c>
       <x:c r="D4" s="0" t="s">
-        <x:v>42</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="E4" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="F4" s="0" t="s">
-        <x:v>44</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="G4" s="0" t="s">
         <x:v>21</x:v>
       </x:c>
       <x:c r="H4" s="0" t="s">
-        <x:v>45</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="I4" s="0" t="s">
         <x:v>36</x:v>
@@ -774,13 +777,13 @@
         <x:v>25</x:v>
       </x:c>
       <x:c r="L4" s="0" t="s">
-        <x:v>46</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="M4" s="0" t="s">
-        <x:v>47</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="N4" s="0" t="s">
-        <x:v>48</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="O4" s="0" t="s">
         <x:v>49</x:v>
@@ -918,7 +921,7 @@
         <x:v>70</x:v>
       </x:c>
       <x:c r="N10" s="0" t="s">
-        <x:v>48</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="O10" s="0" t="s">
         <x:v>71</x:v>

--- a/cypress/downloads/EmployersList.xlsx
+++ b/cypress/downloads/EmployersList.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="67">
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="69">
   <x:si>
     <x:t>Name</x:t>
   </x:si>
@@ -64,6 +64,12 @@
     <x:t>EZMId</x:t>
   </x:si>
   <x:si>
+    <x:t>SecondaryEmail</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IRDNumber</x:t>
+  </x:si>
+  <x:si>
     <x:t>cy new employer</x:t>
   </x:si>
   <x:si>
@@ -103,7 +109,7 @@
     <x:t>Owner nabeel</x:t>
   </x:si>
   <x:si>
-    <x:t>EMP-2BD3-XZXQ</x:t>
+    <x:t>EMP-CAB6-WQBV</x:t>
   </x:si>
   <x:si>
     <x:t>supplier emp</x:t>
@@ -285,9 +291,9 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Grid" displayName="Grid" ref="A1:P11" totalsRowShown="0">
-  <x:autoFilter ref="A1:P11"/>
-  <x:tableColumns count="16">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Grid" displayName="Grid" ref="A1:R11" totalsRowShown="0">
+  <x:autoFilter ref="A1:R11"/>
+  <x:tableColumns count="18">
     <x:tableColumn id="1" name="Name"/>
     <x:tableColumn id="2" name="Email"/>
     <x:tableColumn id="3" name="ContactNo"/>
@@ -304,6 +310,8 @@
     <x:tableColumn id="14" name="Processing Person"/>
     <x:tableColumn id="15" name="Tags"/>
     <x:tableColumn id="16" name="EZMId"/>
+    <x:tableColumn id="17" name="SecondaryEmail"/>
+    <x:tableColumn id="18" name="IRDNumber"/>
   </x:tableColumns>
   <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </x:table>
@@ -597,10 +605,10 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:P11"/>
+  <x:dimension ref="A1:R11"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
-    <x:row r="1" spans="1:16">
+    <x:row r="1" spans="1:18">
       <x:c r="A1" s="0" t="s">
         <x:v>0</x:v>
       </x:c>
@@ -649,292 +657,298 @@
       <x:c r="P1" s="0" t="s">
         <x:v>15</x:v>
       </x:c>
-    </x:row>
-    <x:row r="2" spans="1:16">
+      <x:c r="Q1" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="R1" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="2" spans="1:18">
       <x:c r="A2" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B2" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C2" s="0" t="s">
-        <x:v>18</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="D2" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="E2" s="0" t="s">
-        <x:v>20</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="F2" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="G2" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="H2" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="I2" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="J2" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="K2" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="L2" s="1">
         <x:v>45650</x:v>
       </x:c>
       <x:c r="M2" s="0" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="N2" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="P2" s="0" t="s">
+        <x:v>31</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="3" spans="1:18">
+      <x:c r="A3" s="0" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="B3" s="0" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="C3" s="0" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="D3" s="0" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="E3" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="F3" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="G3" s="0" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="H3" s="0" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="I3" s="0" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="J3" s="0" t="s">
         <x:v>27</x:v>
       </x:c>
-      <x:c r="N2" s="0" t="s">
+      <x:c r="K3" s="0" t="s">
         <x:v>28</x:v>
-      </x:c>
-      <x:c r="P2" s="0" t="s">
-        <x:v>29</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="3" spans="1:16">
-      <x:c r="A3" s="0" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="B3" s="0" t="s">
-        <x:v>31</x:v>
-      </x:c>
-      <x:c r="C3" s="0" t="s">
-        <x:v>18</x:v>
-      </x:c>
-      <x:c r="D3" s="0" t="s">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c r="E3" s="0" t="s">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="F3" s="0" t="s">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="G3" s="0" t="s">
-        <x:v>22</x:v>
-      </x:c>
-      <x:c r="H3" s="0" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="I3" s="0" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="J3" s="0" t="s">
-        <x:v>25</x:v>
-      </x:c>
-      <x:c r="K3" s="0" t="s">
-        <x:v>26</x:v>
       </x:c>
       <x:c r="L3" s="1">
         <x:v>45650</x:v>
       </x:c>
       <x:c r="M3" s="0" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="N3" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="P3" s="0" t="s">
+        <x:v>34</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="4" spans="1:18">
+      <x:c r="A4" s="0" t="s">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="B4" s="0" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="C4" s="0" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="D4" s="0" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="F4" s="0" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="H4" s="0" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="J4" s="0" t="s">
         <x:v>27</x:v>
       </x:c>
-      <x:c r="N3" s="0" t="s">
-        <x:v>28</x:v>
-      </x:c>
-      <x:c r="P3" s="0" t="s">
-        <x:v>32</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="4" spans="1:16">
-      <x:c r="A4" s="0" t="s">
-        <x:v>33</x:v>
-      </x:c>
-      <x:c r="B4" s="0" t="s">
-        <x:v>34</x:v>
-      </x:c>
-      <x:c r="C4" s="0" t="s">
-        <x:v>35</x:v>
-      </x:c>
-      <x:c r="D4" s="0" t="s">
-        <x:v>36</x:v>
-      </x:c>
-      <x:c r="F4" s="0" t="s">
-        <x:v>37</x:v>
-      </x:c>
-      <x:c r="H4" s="0" t="s">
-        <x:v>38</x:v>
-      </x:c>
-      <x:c r="J4" s="0" t="s">
-        <x:v>25</x:v>
-      </x:c>
       <x:c r="K4" s="0" t="s">
-        <x:v>39</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="M4" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="N4" s="0" t="s">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="P4" s="0" t="s">
+        <x:v>44</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5" spans="1:18">
+      <x:c r="A5" s="0" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="I5" s="0" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="J5" s="0" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="K5" s="0" t="s">
         <x:v>41</x:v>
       </x:c>
-      <x:c r="P4" s="0" t="s">
-        <x:v>42</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="5" spans="1:16">
-      <x:c r="A5" s="0" t="s">
-        <x:v>43</x:v>
-      </x:c>
-      <x:c r="I5" s="0" t="s">
+      <x:c r="P5" s="0" t="s">
+        <x:v>46</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6" spans="1:18">
+      <x:c r="A6" s="0" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="B6" s="0" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="C6" s="0" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="D6" s="0" t="s">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="E6" s="0" t="s">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="F6" s="0" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="G6" s="0" t="s">
         <x:v>24</x:v>
       </x:c>
-      <x:c r="J5" s="0" t="s">
-        <x:v>25</x:v>
-      </x:c>
-      <x:c r="K5" s="0" t="s">
-        <x:v>39</x:v>
-      </x:c>
-      <x:c r="P5" s="0" t="s">
-        <x:v>44</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="6" spans="1:16">
-      <x:c r="A6" s="0" t="s">
-        <x:v>45</x:v>
-      </x:c>
-      <x:c r="B6" s="0" t="s">
-        <x:v>46</x:v>
-      </x:c>
-      <x:c r="C6" s="0" t="s">
-        <x:v>47</x:v>
-      </x:c>
-      <x:c r="D6" s="0" t="s">
-        <x:v>48</x:v>
-      </x:c>
-      <x:c r="E6" s="0" t="s">
-        <x:v>49</x:v>
-      </x:c>
-      <x:c r="F6" s="0" t="s">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="G6" s="0" t="s">
-        <x:v>22</x:v>
-      </x:c>
       <x:c r="H6" s="0" t="s">
-        <x:v>51</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="I6" s="0" t="s">
-        <x:v>52</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="J6" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="K6" s="0" t="s">
-        <x:v>39</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="L6" s="1">
         <x:v>45336</x:v>
       </x:c>
       <x:c r="M6" s="0" t="s">
-        <x:v>53</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="N6" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="O6" s="0" t="s">
-        <x:v>54</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="7" spans="1:16">
+        <x:v>56</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7" spans="1:18">
       <x:c r="A7" s="0" t="s">
-        <x:v>55</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="B7" s="0" t="s">
+        <x:v>58</x:v>
+      </x:c>
+      <x:c r="D7" s="0" t="s">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="I7" s="0" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="J7" s="0" t="s">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="K7" s="0" t="s">
+        <x:v>61</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8" spans="1:18">
+      <x:c r="A8" s="0" t="s">
+        <x:v>62</x:v>
+      </x:c>
+      <x:c r="D8" s="0" t="s">
+        <x:v>63</x:v>
+      </x:c>
+      <x:c r="I8" s="0" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="J8" s="0" t="s">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="K8" s="0" t="s">
+        <x:v>61</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" spans="1:18">
+      <x:c r="A9" s="0" t="s">
+        <x:v>64</x:v>
+      </x:c>
+      <x:c r="I9" s="0" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="J9" s="0" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="K9" s="0" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="O9" s="0" t="s">
         <x:v>56</x:v>
       </x:c>
-      <x:c r="D7" s="0" t="s">
-        <x:v>57</x:v>
-      </x:c>
-      <x:c r="I7" s="0" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="J7" s="0" t="s">
-        <x:v>58</x:v>
-      </x:c>
-      <x:c r="K7" s="0" t="s">
-        <x:v>59</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="8" spans="1:16">
-      <x:c r="A8" s="0" t="s">
-        <x:v>60</x:v>
-      </x:c>
-      <x:c r="D8" s="0" t="s">
-        <x:v>61</x:v>
-      </x:c>
-      <x:c r="I8" s="0" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="J8" s="0" t="s">
-        <x:v>58</x:v>
-      </x:c>
-      <x:c r="K8" s="0" t="s">
-        <x:v>59</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="9" spans="1:16">
-      <x:c r="A9" s="0" t="s">
-        <x:v>62</x:v>
-      </x:c>
-      <x:c r="I9" s="0" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="J9" s="0" t="s">
-        <x:v>25</x:v>
-      </x:c>
-      <x:c r="K9" s="0" t="s">
-        <x:v>39</x:v>
-      </x:c>
-      <x:c r="O9" s="0" t="s">
-        <x:v>54</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="10" spans="1:16">
+    </x:row>
+    <x:row r="10" spans="1:18">
       <x:c r="A10" s="0" t="s">
-        <x:v>63</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="I10" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="J10" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="K10" s="0" t="s">
-        <x:v>39</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="L10" s="1">
         <x:v>44984</x:v>
       </x:c>
     </x:row>
-    <x:row r="11" spans="1:16">
+    <x:row r="11" spans="1:18">
       <x:c r="A11" s="0" t="s">
-        <x:v>64</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="I11" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="J11" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="K11" s="0" t="s">
-        <x:v>39</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="L11" s="1">
         <x:v>44952</x:v>
       </x:c>
       <x:c r="N11" s="0" t="s">
-        <x:v>65</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="O11" s="0" t="s">
-        <x:v>66</x:v>
+        <x:v>68</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/cypress/downloads/EmployersList.xlsx
+++ b/cypress/downloads/EmployersList.xlsx
@@ -100,7 +100,7 @@
     <x:t>No</x:t>
   </x:si>
   <x:si>
-    <x:t>Accredited</x:t>
+    <x:t>Unaccredited</x:t>
   </x:si>
   <x:si>
     <x:t>nabeel</x:t>
@@ -109,7 +109,7 @@
     <x:t>Owner nabeel</x:t>
   </x:si>
   <x:si>
-    <x:t>EMP-CAB6-WQBV</x:t>
+    <x:t>EMP-25F2-KA2O</x:t>
   </x:si>
   <x:si>
     <x:t>supplier emp</x:t>
@@ -121,6 +121,9 @@
     <x:t>EMP-CB23-06N4</x:t>
   </x:si>
   <x:si>
+    <x:t>second@gmail.com</x:t>
+  </x:si>
+  <x:si>
     <x:t>mamam</x:t>
   </x:si>
   <x:si>
@@ -137,9 +140,6 @@
   </x:si>
   <x:si>
     <x:t>21</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Unaccredited</x:t>
   </x:si>
   <x:si>
     <x:t>r</x:t>
@@ -757,31 +757,37 @@
       <x:c r="P3" s="0" t="s">
         <x:v>34</x:v>
       </x:c>
+      <x:c r="Q3" s="0" t="s">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="R3" s="0" t="s">
+        <x:v>25</x:v>
+      </x:c>
     </x:row>
     <x:row r="4" spans="1:18">
       <x:c r="A4" s="0" t="s">
-        <x:v>35</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="B4" s="0" t="s">
-        <x:v>36</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="C4" s="0" t="s">
-        <x:v>37</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="D4" s="0" t="s">
-        <x:v>38</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="F4" s="0" t="s">
-        <x:v>39</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="H4" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="J4" s="0" t="s">
         <x:v>27</x:v>
       </x:c>
       <x:c r="K4" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="M4" s="0" t="s">
         <x:v>42</x:v>
@@ -804,7 +810,7 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="K5" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="P5" s="0" t="s">
         <x:v>46</x:v>
@@ -842,7 +848,7 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="K6" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="L6" s="1">
         <x:v>45336</x:v>
@@ -905,7 +911,7 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="K9" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="O9" s="0" t="s">
         <x:v>56</x:v>
@@ -922,7 +928,7 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="K10" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="L10" s="1">
         <x:v>44984</x:v>
@@ -939,7 +945,7 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="K11" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="L11" s="1">
         <x:v>44952</x:v>
